--- a/stories/arbres/ATOM-FAM.SEC.001-03.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est bientôt l'anniversaire de maman. Dahlia est dans sa chambre avec papa. Ils dessinent un grand soleil. Les crayons sentent le bois. Papa dit : c'est une surprise gentille. On la garde un peu. Dahlia sourit. Elle range le dessin sous un livre. Maman entre. Maman dit : ça sent les crayons ici. Dahlia a envie de dire. Papa chuchote : encore un tout petit peu. Le soir, la table est prête. Le dessin est là. Dahlia dit : maman, surprise. C'est pour toi. Maman ouvre les yeux grands. Maman dit : merci Dahlia. Papa dit : une surprise gentille, on la garde un peu, puis on dit. Plus tard, au jardin, papa coupe une petite fleur. Dahlia se souvient. C'est encore une surprise gentille. Elle la garde un peu. Puis on dit. Elle tend la fleur à maman. Même leçon, autre moment. Une surprise gentille se garde un peu, puis on dit.</t>
+          <t>C'est bientôt l'anniversaire de maman. Dahlia est dans sa chambre avec papa. Ils dessinent un grand soleil. Les crayons sentent le bois. C'est une surprise gentille. On la garde un peu. Dahlia sourit. Elle range le dessin sous un livre. Maman entre. Ça sent les crayons ici. Dahlia a envie de dire. Papa chuchote : encore un tout petit peu. Le soir, la table est prête. Le dessin est là. Maman, surprise. C'est pour toi. Maman ouvre les yeux grands. Merci Dahlia. Une surprise gentille, on la garde un peu, puis on dit. Plus tard, au jardin, papa coupe une petite fleur. Dahlia se souvient. C'est encore une surprise gentille. Elle la garde un peu. Puis on dit. Elle tend la fleur à maman. Même leçon, autre moment. Une surprise gentille se garde un peu, puis on dit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,19 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|C'est bientôt l'anniversaire de maman. Dahlia est dans sa chambre avec papa. Ils dessinent un grand soleil. Les crayons sentent le bois.
+papa|C'est une surprise gentille. On la garde un peu.
+narrateur|Dahlia sourit. Elle range le dessin sous un livre. Maman entre.
+maman|Ça sent les crayons ici.
+narrateur|Dahlia a envie de dire. Papa chuchote : encore un tout petit peu. Le soir, la table est prête. Le dessin est là.
+enfant-f|Maman, surprise. C'est pour toi. Maman ouvre les yeux grands.
+maman|Merci Dahlia.
+papa|Une surprise gentille, on la garde un peu, puis on dit. Plus tard, au jardin, papa coupe une petite fleur.
+narrateur|Dahlia se souvient. C'est encore une surprise gentille. Elle la garde un peu. Puis on dit. Elle tend la fleur à maman. Même leçon, autre moment. Une surprise gentille se garde un peu, puis on dit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le dessin pour maman, c'est quoi ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Dahlia a gardé un peu. Puis on dit. Maman a vu le dessin. Plus tard, la fleur aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman pose la fleur dans un verre. Dahlia range un crayon.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.001-03.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.001-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1318,6 +1323,7 @@
 narrateur|Dahlia se souvient. C'est encore une surprise gentille. Elle la garde un peu. Puis on dit. Elle tend la fleur à maman. Même leçon, autre moment. Une surprise gentille se garde un peu, puis on dit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Le dessin pour maman, c'est quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
           <t>narrateur|Dahlia a gardé un peu. Puis on dit. Maman a vu le dessin. Plus tard, la fleur aussi.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1843,7 @@
           <t>narrateur|Maman pose la fleur dans un verre. Dahlia range un crayon.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-FAM.SEC.001-03.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La surprise gentille de Dahlia</t>
+          <t>Le dessin et la fleur de Sarah</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sarah dessine un soleil avec papa. Elle le cache sous un livre. Le soir, elle dit. Plus tard, une fleur du jardin aussi.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est bientôt l'anniversaire de maman. Dahlia est dans sa chambre avec papa. Ils dessinent un grand soleil. Les crayons sentent le bois. C'est une surprise gentille. On la garde un peu. Dahlia sourit. Elle range le dessin sous un livre. Maman entre. Ça sent les crayons ici. Dahlia a envie de dire. Papa chuchote : encore un tout petit peu. Le soir, la table est prête. Le dessin est là. Maman, surprise. C'est pour toi. Maman ouvre les yeux grands. Merci Dahlia. Une surprise gentille, on la garde un peu, puis on dit. Plus tard, au jardin, papa coupe une petite fleur. Dahlia se souvient. C'est encore une surprise gentille. Elle la garde un peu. Puis on dit. Elle tend la fleur à maman. Même leçon, autre moment. Une surprise gentille se garde un peu, puis on dit.</t>
+          <t>Le parquet de la chambre craque tout bas. Un livre est ouvert sur le lit. Les pages sentent le papier tiède. Un signet rouge dépasse un peu. Par la fenêtre, le jardin est vert. Une abeille passe, tout loin. Papa s'assoit par terre, près de Sarah. Les crayons sentent le bois, tu trouves ? Oui, le bois. J'arrive dans un instant. Maman range le linge, plus loin. Bientôt, c'est l'anniversaire de maman. On dessine un grand soleil. Un soleil pour maman. En ce moment, Sarah prend un crayon orange. Le soleil devient grand, tout rond. Des rayons remplissent la feuille. Un rayon plus long, ici. Et un petit, là. Il est pour maman. C'est une surprise gentille. On la garde un peu. On la garde un peu. Sarah glisse le dessin sous le livre. Le livre est lourd, un peu froid. Maman entre. Ça sent les crayons ici. Je garde encore un peu. Encore un tout petit peu. Sarah serre les lèvres. Elle garde encore un peu. Le soir, la table est prête. Le dessin est là, près de l'assiette. Maintenant, on dit. Maman, surprise. C'est pour toi. Maman ouvre les yeux, tout grands. Un soleil. Merci, Sarah. Une surprise gentille, on la garde un peu. Puis on dit. Puis on dit. Plus tard, au jardin, l'herbe est tiède. Un oiseau picore près du cerisier. Papa coupe une petite fleur. La tige est verte, un peu humide. Encore une surprise gentille ? Oui. On la garde un peu. Sarah tient la fleur derrière son dos. Maman arrive près du cerisier. Maman, encore une surprise. C'est pour toi. Une fleur. Merci, ma grande. Même leçon, autre moment. Une surprise gentille se garde un peu. Puis on dit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,18 +1324,71 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|C'est bientôt l'anniversaire de maman. Dahlia est dans sa chambre avec papa. Ils dessinent un grand soleil. Les crayons sentent le bois.
-papa|C'est une surprise gentille. On la garde un peu.
-narrateur|Dahlia sourit. Elle range le dessin sous un livre. Maman entre.
+          <t>narrateur|Le parquet de la chambre craque tout bas.
+narrateur|Un livre est ouvert sur le lit.
+narrateur|Les pages sentent le papier tiède.
+narrateur|Un signet rouge dépasse un peu.
+narrateur|Par la fenêtre, le jardin est vert.
+narrateur|Une abeille passe, tout loin.
+narrateur|Papa s'assoit par terre, près de Sarah.
+papa|Les crayons sentent le bois, tu trouves ?
+enfant-f|Oui, le bois.
+maman|J'arrive dans un instant.
+narrateur|Maman range le linge, plus loin.
+papa|Bientôt, c'est l'anniversaire de maman.
+papa|On dessine un grand soleil.
+enfant-f|Un soleil pour maman.
+narrateur|En ce moment, Sarah prend un crayon orange.
+narrateur|Le soleil devient grand, tout rond.
+narrateur|Des rayons remplissent la feuille.
+papa|Un rayon plus long, ici.
+enfant-f|Et un petit, là.
+enfant-f|Il est pour maman.
+papa|C'est une surprise gentille.
+papa|On la garde un peu.
+enfant-f|On la garde un peu.
+narrateur|Sarah glisse le dessin sous le livre.
+narrateur|Le livre est lourd, un peu froid.
+narrateur|Maman entre.
 maman|Ça sent les crayons ici.
-narrateur|Dahlia a envie de dire. Papa chuchote : encore un tout petit peu. Le soir, la table est prête. Le dessin est là.
-enfant-f|Maman, surprise. C'est pour toi. Maman ouvre les yeux grands.
-maman|Merci Dahlia.
-papa|Une surprise gentille, on la garde un peu, puis on dit. Plus tard, au jardin, papa coupe une petite fleur.
-narrateur|Dahlia se souvient. C'est encore une surprise gentille. Elle la garde un peu. Puis on dit. Elle tend la fleur à maman. Même leçon, autre moment. Une surprise gentille se garde un peu, puis on dit.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+enfant-f|Je garde encore un peu.
+papa|Encore un tout petit peu.
+narrateur|Sarah serre les lèvres.
+narrateur|Elle garde encore un peu.
+narrateur|Le soir, la table est prête.
+narrateur|Le dessin est là, près de l'assiette.
+papa|Maintenant, on dit.
+enfant-f|Maman, surprise.
+enfant-f|C'est pour toi.
+narrateur|Maman ouvre les yeux, tout grands.
+maman|Un soleil.
+maman|Merci, Sarah.
+papa|Une surprise gentille, on la garde un peu.
+papa|Puis on dit.
+enfant-f|Puis on dit.
+narrateur|Plus tard, au jardin, l'herbe est tiède.
+narrateur|Un oiseau picore près du cerisier.
+narrateur|Papa coupe une petite fleur.
+narrateur|La tige est verte, un peu humide.
+enfant-f|Encore une surprise gentille ?
+papa|Oui.
+papa|On la garde un peu.
+narrateur|Sarah tient la fleur derrière son dos.
+narrateur|Maman arrive près du cerisier.
+enfant-f|Maman, encore une surprise.
+enfant-f|C'est pour toi.
+maman|Une fleur.
+maman|Merci, ma grande.
+papa|Même leçon, autre moment.
+papa|Une surprise gentille se garde un peu.
+papa|Puis on dit.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>jardin</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1425,7 +1490,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
@@ -1532,7 +1597,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Dahlia a gardé un peu. Puis on dit. Maman a vu le dessin. Plus tard, la fleur aussi.</t>
+          <t>Sarah a gardé un peu. Puis on dit. Maman a vu le dessin. Plus tard, la fleur aussi. Deux surprises gentilles. Le soleil, puis la fleur. On garde un peu. Puis on dit. Bravo, Sarah. Tu as fait du bon travail. Le cerisier bouge un peu. Tu as gardé, deux fois.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,7 +1741,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Dahlia a gardé un peu. Puis on dit. Maman a vu le dessin. Plus tard, la fleur aussi.</t>
+          <t>narrateur|Sarah a gardé un peu.
+narrateur|Puis on dit.
+narrateur|Maman a vu le dessin.
+narrateur|Plus tard, la fleur aussi.
+papa|Deux surprises gentilles.
+maman|Le soleil, puis la fleur.
+enfant-f|On garde un peu.
+enfant-f|Puis on dit.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+narrateur|Le cerisier bouge un peu.
+papa|Tu as gardé, deux fois.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1704,7 +1780,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman pose la fleur dans un verre. Dahlia range un crayon.</t>
+          <t>Maman pose la fleur dans un verre. L'eau fait un tout petit bruit. Sarah range un crayon. Le parquet craque encore. Le jardin sent l'herbe. Et la fleur sent bon. Oui, un peu sucré. Tu as gardé, puis tu as dit. Deux fois. Deux fois, c'est bien. Le livre est refermé sur le lit. Le signet est encore rouge. On rentre, tout doux. La fleur nous suit.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1840,7 +1916,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman pose la fleur dans un verre. Dahlia range un crayon.</t>
+          <t>narrateur|Maman pose la fleur dans un verre.
+narrateur|L'eau fait un tout petit bruit.
+narrateur|Sarah range un crayon.
+narrateur|Le parquet craque encore.
+papa|Le jardin sent l'herbe.
+enfant-f|Et la fleur sent bon.
+maman|Oui, un peu sucré.
+papa|Tu as gardé, puis tu as dit.
+enfant-f|Deux fois.
+maman|Deux fois, c'est bien.
+narrateur|Le livre est refermé sur le lit.
+enfant-f|Le signet est encore rouge.
+papa|On rentre, tout doux.
+maman|La fleur nous suit.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1868,7 +1957,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a gardé un peu. Puis on a dit. Bravo, Sarah. Le soleil et la fleur. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1929,7 +2018,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
@@ -2008,7 +2097,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a gardé un peu.
+enfant-f|Puis on a dit.
+papa|Bravo, Sarah.
+maman|Le soleil et la fleur.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2030,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2161,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.001-03.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.001-03.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;C'est bientôt l'anniversaire de maman. Dahlia est dans sa chambre avec papa. Ils dessinent un grand soleil. Les crayons sentent le bois. Papa dit : c'est une &lt;emphasis level="moderate"&gt;surprise&lt;/emphasis&gt; gentille. On la garde un peu. Dahlia sourit. Elle range le dessin sous un livre. Maman entre. Maman dit : ça sent les crayons ici. Dahlia a envie de dire. Papa chuchote : encore un tout petit peu. Le soir, la table est prête. Le dessin est là. Dahlia dit : maman, surprise. C'est pour toi. Maman ouvre les yeux grands. Maman dit : merci Dahlia. Papa dit : une surprise gentille, on la garde un peu, puis on dit. Plus tard, au jardin, papa coupe une petite fleur. Dahlia se souvient. C'est encore une surprise gentille. Elle la garde un peu. Puis on dit. Elle tend la fleur à maman. Même leçon, autre moment. Une surprise gentille se garde un peu, puis on dit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le parquet de la chambre craque tout bas. Un livre est ouvert sur le lit. Les pages sentent le papier tiède. Un signet rouge dépasse un peu. Par la fenêtre, le jardin est vert. Une abeille passe, tout loin. Papa s'assoit par terre, près de Sarah. Les crayons sentent le bois, tu trouves ? Oui, le bois. J'arrive dans un instant. Maman range le linge, plus loin. Bientôt, c'est l'anniversaire de maman. On dessine un grand soleil. Un soleil pour maman. En ce moment, Sarah prend un crayon orange. Le soleil devient grand, tout rond. Des rayons remplissent la feuille. Un rayon plus long, ici. Et un petit, là. Il est pour maman. C'est une surprise gentille. On la garde un peu. On la garde un peu. Sarah glisse le dessin sous le livre. Le livre est lourd, un peu froid. Maman entre. Ça sent les crayons ici. Je garde encore un peu. Encore un tout petit peu. Sarah serre les lèvres. Elle garde encore un peu. Le soir, la table est prête. Le dessin est là, près de l'assiette. Maintenant, on dit. Maman, surprise. C'est pour toi. Maman ouvre les yeux, tout grands. Un soleil. Merci, Sarah. Une surprise gentille, on la garde un peu. Puis on dit. Puis on dit. Plus tard, au jardin, l'herbe est tiède. Un oiseau picore près du cerisier. Papa coupe une petite fleur. La tige est verte, un peu humide. Encore une surprise gentille ? Oui. On la garde un peu. Sarah tient la fleur derrière son dos. Maman arrive près du cerisier. Maman, encore une surprise. C'est pour toi. Une fleur. Merci, ma grande. Même leçon, autre moment. Une surprise gentille se garde un peu. Puis on dit.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le dessin pour maman, c'est quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le dessin pour maman, c'est quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1572,7 +1572,6 @@
           <t>narrateur|Le dessin pour maman, c'est quoi ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1597,12 +1596,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah a gardé un peu. Puis on dit. Maman a vu le dessin. Plus tard, la fleur aussi. Deux surprises gentilles. Le soleil, puis la fleur. On garde un peu. Puis on dit. Bravo, Sarah. Tu as fait du bon travail. Le cerisier bouge un peu. Tu as gardé, deux fois.</t>
+          <t>Sarah a gardé un peu. Puis on dit. Maman a vu le dessin. Plus tard, la fleur aussi. Deux surprises gentilles. Le soleil, puis la fleur. On garde un peu. Puis on dit. Bravo, Sarah. Le cerisier bouge un peu. Tu as gardé, deux fois.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Dahlia a gardé un peu. &lt;emphasis level="moderate"&gt;puis&lt;/emphasis&gt; on dit. Maman a vu le dessin. Plus tard, la fleur aussi.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a gardé un peu. Puis on dit. Maman a vu le dessin. Plus tard, la fleur aussi. Deux surprises gentilles. Le soleil, puis la fleur. On garde un peu. Puis on dit. Bravo, Sarah. Le cerisier bouge un peu. Tu as gardé, deux fois.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1750,12 +1749,10 @@
 enfant-f|On garde un peu.
 enfant-f|Puis on dit.
 maman|Bravo, Sarah.
-maman|Tu as fait du bon travail.
 narrateur|Le cerisier bouge un peu.
 papa|Tu as gardé, deux fois.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1785,7 +1782,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman pose la fleur dans un verre. Dahlia range un crayon.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman pose la fleur dans un verre. L'eau fait un tout petit bruit. Sarah range un crayon. Le parquet craque encore. Le jardin sent l'herbe. Et la fleur sent bon. Oui, un peu sucré. Tu as gardé, puis tu as dit. Deux fois. Deux fois, c'est bien. Le livre est refermé sur le lit. Le signet est encore rouge. On rentre, tout doux. La fleur nous suit.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1932,7 +1929,6 @@
 maman|La fleur nous suit.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,12 +1953,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On a gardé un peu. Puis on a dit. Bravo, Sarah. Le soleil et la fleur. L'histoire est finie.</t>
+          <t>On a gardé un peu. Puis on a dit. Bravo, Sarah. Le soleil et la fleur.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>On a gardé un peu. Puis on a dit. Bravo, Sarah. Le soleil et la fleur.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2100,11 +2096,9 @@
           <t>enfant-f|On a gardé un peu.
 enfant-f|Puis on a dit.
 papa|Bravo, Sarah.
-maman|Le soleil et la fleur.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|Le soleil et la fleur.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2123,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2168,6 +2162,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.001-03.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.001-03.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dahlia, papa, maman</t>
+          <t>Sarah, papa, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.001-03.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.001-03.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sarah dessine un soleil avec papa. Elle le cache sous un livre. Le soir, elle dit. Plus tard, une fleur du jardin aussi.</t>
+          <t>Sarah veut un soleil pour l'anniversaire de maman. Elle le cache sous le livre. Le soir, elle le tend. Au jardin, une petite fleur attend derrière son dos. Maman la reçoit.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le parquet de la chambre craque tout bas. Un livre est ouvert sur le lit. Les pages sentent le papier tiède. Un signet rouge dépasse un peu. Par la fenêtre, le jardin est vert. Une abeille passe, tout loin. Papa s'assoit par terre, près de Sarah. Les crayons sentent le bois, tu trouves ? Oui, le bois. J'arrive dans un instant. Maman range le linge, plus loin. Bientôt, c'est l'anniversaire de maman. On dessine un grand soleil. Un soleil pour maman. En ce moment, Sarah prend un crayon orange. Le soleil devient grand, tout rond. Des rayons remplissent la feuille. Un rayon plus long, ici. Et un petit, là. Il est pour maman. C'est une surprise gentille. On la garde un peu. On la garde un peu. Sarah glisse le dessin sous le livre. Le livre est lourd, un peu froid. Maman entre. Ça sent les crayons ici. Je garde encore un peu. Encore un tout petit peu. Sarah serre les lèvres. Elle garde encore un peu. Le soir, la table est prête. Le dessin est là, près de l'assiette. Maintenant, on dit. Maman, surprise. C'est pour toi. Maman ouvre les yeux, tout grands. Un soleil. Merci, Sarah. Une surprise gentille, on la garde un peu. Puis on dit. Puis on dit. Plus tard, au jardin, l'herbe est tiède. Un oiseau picore près du cerisier. Papa coupe une petite fleur. La tige est verte, un peu humide. Encore une surprise gentille ? Oui. On la garde un peu. Sarah tient la fleur derrière son dos. Maman arrive près du cerisier. Maman, encore une surprise. C'est pour toi. Une fleur. Merci, ma grande. Même leçon, autre moment. Une surprise gentille se garde un peu. Puis on dit.</t>
+          <t>Le parquet de la chambre craque tout bas. Un livre est ouvert sur le lit. Les pages sentent le papier tiède. Un signet rouge dépasse un peu. Par la fenêtre, le jardin est vert. Une abeille passe, tout loin. Papa s'assoit par terre, près de Sarah. Les crayons sentent le bois, tu trouves ? Oui, le bois. J'arrive dans un instant. Maman plie le linge, plus loin. Bientôt, c'est l'anniversaire de maman. Je veux un soleil pour elle. Un grand soleil, alors. En ce moment, Sarah prend un crayon orange. Le soleil devient grand, tout rond. Des rayons remplissent la feuille. Un rayon plus long, ici. Et un petit, là. Il est pour maman. On le cache sous le livre ? Oui. Pour tout à l'heure. Sarah glisse le dessin sous le livre. Le livre est lourd, un peu froid. Maman entre. Ça sent les crayons ici. Je garde encore un peu. Encore un tout petit peu ? Oui. Sarah serre les lèvres. Le signet rouge dépasse toujours. Le soir, la table est prête. Le dessin est là, près de l'assiette. C'est le moment, Sarah ? Maman, surprise. C'est pour toi. Maman ouvre les yeux, tout grands. Un soleil. Merci, Sarah. Il a un petit rayon, là. Je le vois. Plus tard, au jardin, l'herbe est tiède. Un oiseau picore près du cerisier. Papa coupe une petite fleur. La tige est verte, un peu humide. Pour maman, encore ? Si tu veux. Tu la tiens derrière toi ? Oui. Sarah tient la fleur derrière son dos. Une goutte glisse sur son doigt. Maman arrive près du cerisier. Maman, c'est pour toi. Sarah tend la fleur. Une fleur. Merci, ma grande. Elle sent bon, tu trouves ? Un peu sucré. Le cerisier bouge un peu. L'abeille n'est plus là.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Le parquet de la chambre craque tout bas. Un livre est ouvert sur le lit. Les pages sentent le papier tiède. Un signet rouge dépasse un peu. Par la fenêtre, le jardin est vert. Une abeille passe, tout loin. Papa s'assoit par terre, près de Sarah. Les crayons sentent le bois, tu trouves ? Oui, le bois. J'arrive dans un instant. Maman range le linge, plus loin. Bientôt, c'est l'anniversaire de maman. On dessine un grand soleil. Un soleil pour maman. En ce moment, Sarah prend un crayon orange. Le soleil devient grand, tout rond. Des rayons remplissent la feuille. Un rayon plus long, ici. Et un petit, là. Il est pour maman. C'est une surprise gentille. On la garde un peu. On la garde un peu. Sarah glisse le dessin sous le livre. Le livre est lourd, un peu froid. Maman entre. Ça sent les crayons ici. Je garde encore un peu. Encore un tout petit peu. Sarah serre les lèvres. Elle garde encore un peu. Le soir, la table est prête. Le dessin est là, près de l'assiette. Maintenant, on dit. Maman, surprise. C'est pour toi. Maman ouvre les yeux, tout grands. Un soleil. Merci, Sarah. Une surprise gentille, on la garde un peu. Puis on dit. Puis on dit. Plus tard, au jardin, l'herbe est tiède. Un oiseau picore près du cerisier. Papa coupe une petite fleur. La tige est verte, un peu humide. Encore une surprise gentille ? Oui. On la garde un peu. Sarah tient la fleur derrière son dos. Maman arrive près du cerisier. Maman, encore une surprise. C'est pour toi. Une fleur. Merci, ma grande. Même leçon, autre moment. Une surprise gentille se garde un peu. Puis on dit.</t>
+          <t>Le parquet de la chambre craque tout bas. Un livre est ouvert sur le lit. Les pages sentent le papier tiède. Un signet rouge dépasse un peu. Par la fenêtre, le jardin est vert. Une abeille passe, tout loin. Papa s'assoit par terre, près de Sarah. Les crayons sentent le bois, tu trouves ? Oui, le bois. J'arrive dans un instant. Maman plie le linge, plus loin. Bientôt, c'est l'anniversaire de maman. Je veux un soleil pour elle. Un grand soleil, alors. En ce moment, Sarah prend un crayon orange. Le soleil devient grand, tout rond. Des rayons remplissent la feuille. Un rayon plus long, ici. Et un petit, là. Il est pour maman. On le cache sous le livre ? Oui. Pour tout à l'heure. Sarah glisse le dessin sous le livre. Le livre est lourd, un peu froid. Maman entre. Ça sent les crayons ici. Je garde encore un peu. Encore un tout petit peu ? Oui. Sarah serre les lèvres. Le signet rouge dépasse toujours. Le soir, la table est prête. Le dessin est là, près de l'assiette. C'est le moment, Sarah ? Maman, surprise. C'est pour toi. Maman ouvre les yeux, tout grands. Un soleil. Merci, Sarah. Il a un petit rayon, là. Je le vois. Plus tard, au jardin, l'herbe est tiède. Un oiseau picore près du cerisier. Papa coupe une petite fleur. La tige est verte, un peu humide. Pour maman, encore ? Si tu veux. Tu la tiens derrière toi ? Oui. Sarah tient la fleur derrière son dos. Une goutte glisse sur son doigt. Maman arrive près du cerisier. Maman, c'est pour toi. Sarah tend la fleur. Une fleur. Merci, ma grande. Elle sent bon, tu trouves ? Un peu sucré. Le cerisier bouge un peu. L'abeille n'est plus là.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1334,54 +1334,57 @@
 papa|Les crayons sentent le bois, tu trouves ?
 enfant-f|Oui, le bois.
 maman|J'arrive dans un instant.
-narrateur|Maman range le linge, plus loin.
+narrateur|Maman plie le linge, plus loin.
 papa|Bientôt, c'est l'anniversaire de maman.
-papa|On dessine un grand soleil.
-enfant-f|Un soleil pour maman.
+enfant-f|Je veux un soleil pour elle.
+papa|Un grand soleil, alors.
 narrateur|En ce moment, Sarah prend un crayon orange.
 narrateur|Le soleil devient grand, tout rond.
 narrateur|Des rayons remplissent la feuille.
 papa|Un rayon plus long, ici.
 enfant-f|Et un petit, là.
 enfant-f|Il est pour maman.
-papa|C'est une surprise gentille.
-papa|On la garde un peu.
-enfant-f|On la garde un peu.
+papa|On le cache sous le livre ?
+enfant-f|Oui.
+enfant-f|Pour tout à l'heure.
 narrateur|Sarah glisse le dessin sous le livre.
 narrateur|Le livre est lourd, un peu froid.
 narrateur|Maman entre.
 maman|Ça sent les crayons ici.
 enfant-f|Je garde encore un peu.
-papa|Encore un tout petit peu.
+papa|Encore un tout petit peu ?
+enfant-f|Oui.
 narrateur|Sarah serre les lèvres.
-narrateur|Elle garde encore un peu.
+narrateur|Le signet rouge dépasse toujours.
 narrateur|Le soir, la table est prête.
 narrateur|Le dessin est là, près de l'assiette.
-papa|Maintenant, on dit.
+papa|C'est le moment, Sarah ?
 enfant-f|Maman, surprise.
 enfant-f|C'est pour toi.
 narrateur|Maman ouvre les yeux, tout grands.
 maman|Un soleil.
 maman|Merci, Sarah.
-papa|Une surprise gentille, on la garde un peu.
-papa|Puis on dit.
-enfant-f|Puis on dit.
+enfant-f|Il a un petit rayon, là.
+maman|Je le vois.
 narrateur|Plus tard, au jardin, l'herbe est tiède.
 narrateur|Un oiseau picore près du cerisier.
 narrateur|Papa coupe une petite fleur.
 narrateur|La tige est verte, un peu humide.
-enfant-f|Encore une surprise gentille ?
-papa|Oui.
-papa|On la garde un peu.
+enfant-f|Pour maman, encore ?
+papa|Si tu veux.
+papa|Tu la tiens derrière toi ?
+enfant-f|Oui.
 narrateur|Sarah tient la fleur derrière son dos.
+narrateur|Une goutte glisse sur son doigt.
 narrateur|Maman arrive près du cerisier.
-enfant-f|Maman, encore une surprise.
-enfant-f|C'est pour toi.
+enfant-f|Maman, c'est pour toi.
+narrateur|Sarah tend la fleur.
 maman|Une fleur.
 maman|Merci, ma grande.
-papa|Même leçon, autre moment.
-papa|Une surprise gentille se garde un peu.
-papa|Puis on dit.</t>
+papa|Elle sent bon, tu trouves ?
+enfant-f|Un peu sucré.
+narrateur|Le cerisier bouge un peu.
+narrateur|L'abeille n'est plus là.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1448,7 +1451,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>C'est une surprise gentille. C'est quoi ?</t>
+          <t>Sarah cache le dessin. C'est quoi, pour maman ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1497,7 +1500,7 @@
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1596,12 +1599,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah a gardé un peu. Puis on dit. Maman a vu le dessin. Plus tard, la fleur aussi. Deux surprises gentilles. Le soleil, puis la fleur. On garde un peu. Puis on dit. Bravo, Sarah. Le cerisier bouge un peu. Tu as gardé, deux fois.</t>
+          <t>Maman pose la fleur dans un verre. L'eau fait un tout petit bruit. Le soleil reste près de l'assiette ? Oui. Deux cadeaux. Bravo, Sarah. Le dessin, puis la fleur. Oui. Le cerisier bouge un peu. Une feuille tombe dans l'herbe.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Sarah a gardé un peu. Puis on dit. Maman a vu le dessin. Plus tard, la fleur aussi. Deux surprises gentilles. Le soleil, puis la fleur. On garde un peu. Puis on dit. Bravo, Sarah. Le cerisier bouge un peu. Tu as gardé, deux fois.</t>
+          <t>Maman pose la fleur dans un verre. L'eau fait un tout petit bruit. Le soleil reste près de l'assiette ? Oui. Deux cadeaux. Bravo, Sarah. Le dessin, puis la fleur. Oui. Le cerisier bouge un peu. Une feuille tombe dans l'herbe.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1664,7 +1667,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1740,17 +1743,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sarah a gardé un peu.
-narrateur|Puis on dit.
-narrateur|Maman a vu le dessin.
-narrateur|Plus tard, la fleur aussi.
-papa|Deux surprises gentilles.
-maman|Le soleil, puis la fleur.
-enfant-f|On garde un peu.
-enfant-f|Puis on dit.
+          <t>narrateur|Maman pose la fleur dans un verre.
+narrateur|L'eau fait un tout petit bruit.
+papa|Le soleil reste près de l'assiette ?
+enfant-f|Oui.
+maman|Deux cadeaux.
 maman|Bravo, Sarah.
+enfant-f|Le dessin, puis la fleur.
+papa|Oui.
 narrateur|Le cerisier bouge un peu.
-papa|Tu as gardé, deux fois.</t>
+narrateur|Une feuille tombe dans l'herbe.</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1779,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman pose la fleur dans un verre. L'eau fait un tout petit bruit. Sarah range un crayon. Le parquet craque encore. Le jardin sent l'herbe. Et la fleur sent bon. Oui, un peu sucré. Tu as gardé, puis tu as dit. Deux fois. Deux fois, c'est bien. Le livre est refermé sur le lit. Le signet est encore rouge. On rentre, tout doux. La fleur nous suit.</t>
+          <t>Sarah range un crayon. Le parquet craque encore. Le jardin sent l'herbe. Et la fleur sent bon. Oui, un peu sucré. On rentre, tout doux ? Oui. Le signet est encore rouge. La fleur nous suit. Le livre est refermé sur le lit. Le verre tremble un peu, dans la main de maman.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Maman pose la fleur dans un verre. L'eau fait un tout petit bruit. Sarah range un crayon. Le parquet craque encore. Le jardin sent l'herbe. Et la fleur sent bon. Oui, un peu sucré. Tu as gardé, puis tu as dit. Deux fois. Deux fois, c'est bien. Le livre est refermé sur le lit. Le signet est encore rouge. On rentre, tout doux. La fleur nous suit.</t>
+          <t>Sarah range un crayon. Le parquet craque encore. Le jardin sent l'herbe. Et la fleur sent bon. Oui, un peu sucré. On rentre, tout doux ? Oui. Le signet est encore rouge. La fleur nous suit. Le livre est refermé sur le lit. Le verre tremble un peu, dans la main de maman.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1845,7 +1847,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1913,20 +1915,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman pose la fleur dans un verre.
-narrateur|L'eau fait un tout petit bruit.
-narrateur|Sarah range un crayon.
+          <t>narrateur|Sarah range un crayon.
 narrateur|Le parquet craque encore.
 papa|Le jardin sent l'herbe.
 enfant-f|Et la fleur sent bon.
 maman|Oui, un peu sucré.
-papa|Tu as gardé, puis tu as dit.
-enfant-f|Deux fois.
-maman|Deux fois, c'est bien.
+papa|On rentre, tout doux ?
+enfant-f|Oui.
+enfant-f|Le signet est encore rouge.
+maman|La fleur nous suit.
 narrateur|Le livre est refermé sur le lit.
-enfant-f|Le signet est encore rouge.
-papa|On rentre, tout doux.
-maman|La fleur nous suit.</t>
+narrateur|Le verre tremble un peu, dans la main de maman.</t>
         </is>
       </c>
     </row>
@@ -1953,12 +1952,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On a gardé un peu. Puis on a dit. Bravo, Sarah. Le soleil et la fleur.</t>
+          <t>Le soleil est pour toi. Merci, Sarah. La fleur tient dans le verre. L'eau est claire, tout calme.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>On a gardé un peu. Puis on a dit. Bravo, Sarah. Le soleil et la fleur.</t>
+          <t>Le soleil est pour toi. Merci, Sarah. La fleur tient dans le verre. L'eau est claire, tout calme.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2014,14 +2013,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2093,10 +2092,10 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-f|On a gardé un peu.
-enfant-f|Puis on a dit.
-papa|Bravo, Sarah.
-maman|Le soleil et la fleur.</t>
+          <t>enfant-f|Le soleil est pour toi.
+maman|Merci, Sarah.
+narrateur|La fleur tient dans le verre.
+narrateur|L'eau est claire, tout calme.</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2167,6 +2166,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
